--- a/diseases/d013/1980-1984.xlsx
+++ b/diseases/d013/1980-1984.xlsx
@@ -1545,6 +1545,11 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
@@ -1562,7 +1567,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1572,6 +1582,11 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1637,7 +1652,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1672,12 +1687,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1981-02-01</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1981-02</t>
+          <t>1981-01</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1691,11 +1706,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1703,7 +1801,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1713,6 +1816,11 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1813,19 +1921,24 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1981-03-01</t>
+          <t>1981-02-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1981-03</t>
+          <t>1981-02</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1844,7 +1957,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1854,6 +1972,11 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1919,7 +2042,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1954,12 +2077,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1981-04-01</t>
+          <t>1981-02-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1981-04</t>
+          <t>1981-02</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1973,11 +2096,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1985,7 +2191,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1995,6 +2206,11 @@
       </c>
       <c r="AT9" t="n">
         <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2095,19 +2311,24 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1981-05-01</t>
+          <t>1981-03-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1981-05</t>
+          <t>1981-03</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2126,7 +2347,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2136,6 +2362,11 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2201,7 +2432,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2236,30 +2467,113 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1981-06-01</t>
+          <t>1981-03-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1981-06</t>
+          <t>1981-03</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2267,7 +2581,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2277,6 +2596,11 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2377,12 +2701,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1981-07-01</t>
+          <t>1981-04-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1981-07</t>
+          <t>1981-04</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2391,6 +2715,11 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
@@ -2408,7 +2737,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2418,6 +2752,11 @@
       </c>
       <c r="AT12" t="n">
         <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2483,7 +2822,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2518,12 +2857,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1981-08-01</t>
+          <t>1981-04-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1981-08</t>
+          <t>1981-04</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2537,11 +2876,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2549,7 +2971,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2559,6 +2986,11 @@
       </c>
       <c r="AT13" t="n">
         <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2659,12 +3091,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1981-09-01</t>
+          <t>1981-05-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1981-09</t>
+          <t>1981-05</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2673,6 +3105,11 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
@@ -2690,7 +3127,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2700,6 +3142,11 @@
       </c>
       <c r="AT14" t="n">
         <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2765,7 +3212,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2800,12 +3247,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1981-10-01</t>
+          <t>1981-05-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1981-10</t>
+          <t>1981-05</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2819,11 +3266,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2831,7 +3361,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2841,6 +3376,11 @@
       </c>
       <c r="AT15" t="n">
         <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2941,12 +3481,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1981-11-01</t>
+          <t>1981-06-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1981-11</t>
+          <t>1981-06</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2955,6 +3495,11 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
@@ -2972,7 +3517,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -2982,6 +3532,11 @@
       </c>
       <c r="AT16" t="n">
         <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3047,7 +3602,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3082,12 +3637,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1981-12-01</t>
+          <t>1981-06-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1981-12</t>
+          <t>1981-06</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3101,11 +3656,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3113,7 +3751,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3123,6 +3766,11 @@
       </c>
       <c r="AT17" t="n">
         <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3193,12 +3841,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3223,12 +3871,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1981-07-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1982-01</t>
+          <t>1981-07</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3244,12 +3892,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3269,7 +3917,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -3282,42 +3930,42 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3997,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3379,12 +4027,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1981-07-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1982-01</t>
+          <t>1981-07</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3395,22 +4043,22 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Poliomyelitt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3420,12 +4068,12 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3435,7 +4083,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>country:CA:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3470,12 +4118,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -3503,7 +4151,7 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
@@ -3516,42 +4164,42 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -3613,12 +4261,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1981-08-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1982-01</t>
+          <t>1981-08</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3627,6 +4275,11 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
@@ -3644,7 +4297,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -3654,6 +4312,11 @@
       </c>
       <c r="AT20" t="n">
         <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3719,7 +4382,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3754,12 +4417,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1982-02-01</t>
+          <t>1981-08-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1982-02</t>
+          <t>1981-08</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3773,11 +4436,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3785,7 +4531,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -3795,6 +4546,11 @@
       </c>
       <c r="AT21" t="n">
         <v>1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3895,12 +4651,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1982-03-01</t>
+          <t>1981-09-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1982-03</t>
+          <t>1981-09</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3909,6 +4665,11 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
@@ -3926,7 +4687,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -3936,6 +4702,11 @@
       </c>
       <c r="AT22" t="n">
         <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4001,7 +4772,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4036,12 +4807,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1982-04-01</t>
+          <t>1981-09-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1982-04</t>
+          <t>1981-09</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4055,11 +4826,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4067,7 +4921,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -4077,6 +4936,11 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4177,12 +5041,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1982-05-01</t>
+          <t>1981-10-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1982-05</t>
+          <t>1981-10</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4191,6 +5055,11 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
@@ -4208,7 +5077,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4218,6 +5092,11 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4283,7 +5162,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4318,12 +5197,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1982-06-01</t>
+          <t>1981-10-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1982-06</t>
+          <t>1981-10</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4337,11 +5216,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN25" t="b">
+        <v>1</v>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4349,7 +5311,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4359,6 +5326,11 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4459,12 +5431,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1982-07-01</t>
+          <t>1981-11-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1982-07</t>
+          <t>1981-11</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4473,6 +5445,11 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
@@ -4490,7 +5467,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4500,6 +5482,11 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4565,7 +5552,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4600,12 +5587,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1982-08-01</t>
+          <t>1981-11-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1982-08</t>
+          <t>1981-11</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4619,11 +5606,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
+        <v>1</v>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4631,7 +5701,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4641,6 +5716,11 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4741,12 +5821,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1982-09-01</t>
+          <t>1981-12-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1982-09</t>
+          <t>1981-12</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4755,6 +5835,11 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_109_MONTHLY</t>
@@ -4772,7 +5857,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -4782,6 +5872,11 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4847,7 +5942,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4882,12 +5977,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1982-10-01</t>
+          <t>1981-12-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1982-10</t>
+          <t>1981-12</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4901,11 +5996,94 @@
           <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4913,7 +6091,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -4923,6 +6106,11 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4993,12 +6181,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5023,12 +6211,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1982-11-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1982-11</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5037,14 +6225,19 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_109_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5054,55 +6247,65 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_109_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
         </is>
       </c>
       <c r="AT30" t="n">
         <v>1</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5129,17 +6332,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5164,30 +6367,113 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1982-12-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1982-12</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
         <v>1</v>
       </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_109_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -5195,55 +6481,65 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_109_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
         </is>
       </c>
       <c r="AT31" t="n">
         <v>1</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5275,12 +6571,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5305,12 +6601,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1983-01</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5326,12 +6622,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5351,7 +6647,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -5364,42 +6660,42 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -5431,12 +6727,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5461,12 +6757,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1983-01</t>
+          <t>1982-01</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5477,22 +6773,22 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Poliomyelitt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -5502,12 +6798,12 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -5517,7 +6813,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>country:CA:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5552,12 +6848,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -5585,7 +6881,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -5598,42 +6894,42 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -5665,12 +6961,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5695,19 +6991,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1982-02-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1982-02</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5716,12 +7012,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5741,7 +7037,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -5754,42 +7050,42 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -5821,12 +7117,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5851,38 +7147,38 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1984-01-01</t>
+          <t>1982-02-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1984-01</t>
+          <t>1982-02</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Poliomyelitis</t>
+          <t>Poliomyelitt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -5892,12 +7188,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5907,7 +7203,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>country:CA:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -5942,12 +7238,12 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -5975,7 +7271,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_NO_FHI_109_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -5988,40 +7284,4720 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1982-03-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>1982-03</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1982-03-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>1982-03</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW35" t="inlineStr">
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1982-04-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1982-04</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1982-04-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1982-04</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1982-05-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1982-05</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1982-05-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1982-05</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1982-06-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1982-06</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1982-06-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1982-06</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1982-07-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1982-07</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1982-07-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1982-07</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1982-08-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1982-08</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1982-08-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1982-08</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1982-09-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>1982-09</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1982-09-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1982-09</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1982-10-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1982-10</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1982-10-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1982-10</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1982-11-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1982-11</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1982-11-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1982-11</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1982-12-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1982-12</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1982-12-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1982-12</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Poliomyelitt</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_109_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1983-01</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
         <is>
           <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX56" t="inlineStr">
         <is>
           <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr">
+      <c r="AY56" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="BA35" t="inlineStr">
+      <c r="BA56" t="inlineStr">
         <is>
           <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
-      <c r="BB35" t="inlineStr">
+      <c r="BB56" t="inlineStr">
         <is>
           <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1983-01</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1984-01</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>1984-01</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Canada PHAC CNDSS Annual</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -6153,7 +12129,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -6173,7 +12149,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -6183,7 +12159,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
